--- a/assets/checklist-template.xlsx
+++ b/assets/checklist-template.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20391"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF26267D-0FFE-4393-83CB-4BC635E6294E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F0E68EB4-3A2D-4875-AEDF-DA55FE546919}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17040" windowHeight="7520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Чек-лист макет" sheetId="1" r:id="rId1"/>
@@ -22,15 +22,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -41,7 +32,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="E4" authorId="0" shapeId="0" xr:uid="{EAA57E07-19AE-4FD8-BA93-BEAB70A25A7B}">
+    <comment ref="E5" authorId="0" shapeId="0" xr:uid="{EAA57E07-19AE-4FD8-BA93-BEAB70A25A7B}">
       <text>
         <r>
           <rPr>
@@ -179,7 +170,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E5" authorId="0" shapeId="0" xr:uid="{3FCB6E3D-598E-43F0-8348-456D857741A1}">
+    <comment ref="E6" authorId="0" shapeId="0" xr:uid="{3FCB6E3D-598E-43F0-8348-456D857741A1}">
       <text>
         <r>
           <rPr>
@@ -295,7 +286,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{32C8E329-AFC0-4D84-9ECC-54040DEC627D}">
+    <comment ref="E9" authorId="0" shapeId="0" xr:uid="{32C8E329-AFC0-4D84-9ECC-54040DEC627D}">
       <text>
         <r>
           <rPr>
@@ -375,7 +366,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E8" authorId="0" shapeId="0" xr:uid="{E552D9B6-F163-4929-8FD6-32414521FCF1}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{E552D9B6-F163-4929-8FD6-32414521FCF1}">
       <text>
         <r>
           <rPr>
@@ -453,7 +444,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E9" authorId="0" shapeId="0" xr:uid="{246B0787-E5EC-44DE-B2FA-7F65FBC9F4AA}">
+    <comment ref="E11" authorId="0" shapeId="0" xr:uid="{246B0787-E5EC-44DE-B2FA-7F65FBC9F4AA}">
       <text>
         <r>
           <rPr>
@@ -527,7 +518,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{A4510A72-9F5F-4A88-8DF5-67C458DAA6EE}">
+    <comment ref="E12" authorId="0" shapeId="0" xr:uid="{A4510A72-9F5F-4A88-8DF5-67C458DAA6EE}">
       <text>
         <r>
           <rPr>
@@ -614,7 +605,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E11" authorId="0" shapeId="0" xr:uid="{C809E9A7-F270-43BC-B408-9DB09771596E}">
+    <comment ref="E13" authorId="0" shapeId="0" xr:uid="{C809E9A7-F270-43BC-B408-9DB09771596E}">
       <text>
         <r>
           <rPr>
@@ -735,7 +726,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E12" authorId="0" shapeId="0" xr:uid="{FB21D1B6-07C4-4AB5-AC25-B3E85A475604}">
+    <comment ref="E14" authorId="0" shapeId="0" xr:uid="{FB21D1B6-07C4-4AB5-AC25-B3E85A475604}">
       <text>
         <r>
           <rPr>
@@ -851,7 +842,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E14" authorId="0" shapeId="0" xr:uid="{BFA49DAA-DA3E-40C1-A07D-98109E810DF1}">
+    <comment ref="E16" authorId="0" shapeId="0" xr:uid="{BFA49DAA-DA3E-40C1-A07D-98109E810DF1}">
       <text>
         <r>
           <rPr>
@@ -923,7 +914,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E15" authorId="0" shapeId="0" xr:uid="{DE827F92-9F80-4511-A392-F1352E563EBC}">
+    <comment ref="E17" authorId="0" shapeId="0" xr:uid="{DE827F92-9F80-4511-A392-F1352E563EBC}">
       <text>
         <r>
           <rPr>
@@ -996,7 +987,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E17" authorId="0" shapeId="0" xr:uid="{6D1F3F59-D325-4E56-B182-975945CB3A7D}">
+    <comment ref="E19" authorId="0" shapeId="0" xr:uid="{6D1F3F59-D325-4E56-B182-975945CB3A7D}">
       <text>
         <r>
           <rPr>
@@ -1076,7 +1067,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E19" authorId="0" shapeId="0" xr:uid="{0F875692-258B-4122-AF8F-09EFE37C01E9}">
+    <comment ref="E21" authorId="0" shapeId="0" xr:uid="{0F875692-258B-4122-AF8F-09EFE37C01E9}">
       <text>
         <r>
           <rPr>
@@ -1155,7 +1146,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E20" authorId="0" shapeId="0" xr:uid="{03733007-1290-4018-9E1E-85A19F1AC81C}">
+    <comment ref="E22" authorId="0" shapeId="0" xr:uid="{03733007-1290-4018-9E1E-85A19F1AC81C}">
       <text>
         <r>
           <rPr>
@@ -1239,7 +1230,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E21" authorId="0" shapeId="0" xr:uid="{5877AA62-4388-4472-9158-E184FE92FBF6}">
+    <comment ref="E23" authorId="0" shapeId="0" xr:uid="{5877AA62-4388-4472-9158-E184FE92FBF6}">
       <text>
         <r>
           <rPr>
@@ -1317,7 +1308,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E23" authorId="0" shapeId="0" xr:uid="{E10B083B-A34F-41D0-B267-2D57465D434C}">
+    <comment ref="E25" authorId="0" shapeId="0" xr:uid="{E10B083B-A34F-41D0-B267-2D57465D434C}">
       <text>
         <r>
           <rPr>
@@ -1400,7 +1391,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E24" authorId="0" shapeId="0" xr:uid="{4D82A118-B54B-4EF4-AB5A-403497EC513A}">
+    <comment ref="E26" authorId="0" shapeId="0" xr:uid="{4D82A118-B54B-4EF4-AB5A-403497EC513A}">
       <text>
         <r>
           <rPr>
@@ -1472,7 +1463,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E26" authorId="0" shapeId="0" xr:uid="{99C1C587-9D03-4855-8AC5-3804C6547A4C}">
+    <comment ref="E28" authorId="0" shapeId="0" xr:uid="{99C1C587-9D03-4855-8AC5-3804C6547A4C}">
       <text>
         <r>
           <rPr>
@@ -1519,7 +1510,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E27" authorId="0" shapeId="0" xr:uid="{8AAF7FA4-0313-4F99-A741-B4BBB1FAD1E2}">
+    <comment ref="E29" authorId="0" shapeId="0" xr:uid="{8AAF7FA4-0313-4F99-A741-B4BBB1FAD1E2}">
       <text>
         <r>
           <rPr>
@@ -1567,7 +1558,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E28" authorId="0" shapeId="0" xr:uid="{DCAADCFB-D9DA-4630-8156-98E6D02460EB}">
+    <comment ref="E30" authorId="0" shapeId="0" xr:uid="{DCAADCFB-D9DA-4630-8156-98E6D02460EB}">
       <text>
         <r>
           <rPr>
@@ -1616,7 +1607,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E29" authorId="0" shapeId="0" xr:uid="{42C88E2F-0897-45B3-8F01-3D83C52229FB}">
+    <comment ref="E31" authorId="0" shapeId="0" xr:uid="{42C88E2F-0897-45B3-8F01-3D83C52229FB}">
       <text>
         <r>
           <rPr>
@@ -1664,7 +1655,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E31" authorId="0" shapeId="0" xr:uid="{07399DC1-82C1-4E08-9B0F-93FDE4322581}">
+    <comment ref="E33" authorId="0" shapeId="0" xr:uid="{07399DC1-82C1-4E08-9B0F-93FDE4322581}">
       <text>
         <r>
           <rPr>
@@ -1690,7 +1681,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E32" authorId="0" shapeId="0" xr:uid="{68F74A0B-594D-44E2-B870-3B46EB03F8E3}">
+    <comment ref="E34" authorId="0" shapeId="0" xr:uid="{68F74A0B-594D-44E2-B870-3B46EB03F8E3}">
       <text>
         <r>
           <rPr>
@@ -1716,7 +1707,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E33" authorId="0" shapeId="0" xr:uid="{DBB78AE9-3245-4447-9BFA-B32721B6C67C}">
+    <comment ref="E35" authorId="0" shapeId="0" xr:uid="{DBB78AE9-3245-4447-9BFA-B32721B6C67C}">
       <text>
         <r>
           <rPr>
@@ -1742,7 +1733,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E35" authorId="0" shapeId="0" xr:uid="{7A3E192A-9161-4F4D-9BAD-07C56918C73E}">
+    <comment ref="E37" authorId="0" shapeId="0" xr:uid="{7A3E192A-9161-4F4D-9BAD-07C56918C73E}">
       <text>
         <r>
           <rPr>
@@ -1768,7 +1759,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E36" authorId="0" shapeId="0" xr:uid="{B5FE78C7-B3F1-40A8-8638-18DCD2934150}">
+    <comment ref="E38" authorId="0" shapeId="0" xr:uid="{B5FE78C7-B3F1-40A8-8638-18DCD2934150}">
       <text>
         <r>
           <rPr>
@@ -1807,7 +1798,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E37" authorId="0" shapeId="0" xr:uid="{7BA6CD0E-4DB5-4F82-8108-FAD22554224F}">
+    <comment ref="E39" authorId="0" shapeId="0" xr:uid="{7BA6CD0E-4DB5-4F82-8108-FAD22554224F}">
       <text>
         <r>
           <rPr>
@@ -1832,7 +1823,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E38" authorId="0" shapeId="0" xr:uid="{47851D8F-28D9-48AF-86B7-D718B23A57CC}">
+    <comment ref="E40" authorId="0" shapeId="0" xr:uid="{47851D8F-28D9-48AF-86B7-D718B23A57CC}">
       <text>
         <r>
           <rPr>
@@ -1903,7 +1894,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="143">
   <si>
     <t>Приветствие</t>
   </si>
@@ -2329,6 +2320,9 @@
   </si>
   <si>
     <t>Результат_4</t>
+  </si>
+  <si>
+    <t>Сверка города</t>
   </si>
 </sst>
 </file>
@@ -2545,7 +2539,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="37">
+  <borders count="36">
     <border>
       <left/>
       <right/>
@@ -2682,6 +2676,17 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thin">
         <color theme="0"/>
@@ -2758,6 +2763,17 @@
         <color indexed="64"/>
       </left>
       <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -2842,6 +2858,17 @@
     </border>
     <border>
       <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right/>
       <top/>
       <bottom style="thin">
@@ -2878,6 +2905,50 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color rgb="FF33CCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF33CCCC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF33CCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF33CCCC"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF33CCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF33CCCC"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF33CCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF33CCCC"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -2903,114 +2974,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF33CCCC"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF33CCCC"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF33CCCC"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF33CCCC"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF33CCCC"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF33CCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF33CCCC"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF33CCCC"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF33CCCC"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3043,13 +3012,16 @@
     <xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3078,7 +3050,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3096,20 +3068,20 @@
     <xf numFmtId="9" fontId="1" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3118,7 +3090,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="2" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3133,153 +3108,168 @@
     <xf numFmtId="9" fontId="1" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="16" fillId="4" borderId="35" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="16" fillId="4" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3906,31 +3896,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R48"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:R50"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.21875" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="15.44140625" customWidth="1"/>
-    <col min="3" max="3" width="8.77734375" customWidth="1"/>
-    <col min="4" max="4" width="20.33203125" customWidth="1"/>
-    <col min="5" max="5" width="44.77734375" customWidth="1"/>
-    <col min="6" max="6" width="23.77734375" customWidth="1"/>
-    <col min="7" max="7" width="27.44140625" customWidth="1"/>
-    <col min="8" max="8" width="28.88671875" customWidth="1"/>
-    <col min="9" max="9" width="11.6640625" customWidth="1"/>
-    <col min="10" max="10" width="52.44140625" customWidth="1"/>
-    <col min="11" max="11" width="22.44140625" customWidth="1"/>
-    <col min="12" max="12" width="52.44140625" customWidth="1"/>
+    <col min="1" max="1" width="4.08984375" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="15.453125" customWidth="1"/>
+    <col min="3" max="3" width="8.7265625" customWidth="1"/>
+    <col min="4" max="4" width="20.36328125" customWidth="1"/>
+    <col min="5" max="5" width="44.81640625" customWidth="1"/>
+    <col min="6" max="6" width="23.81640625" customWidth="1"/>
+    <col min="7" max="7" width="12.453125" customWidth="1"/>
+    <col min="8" max="8" width="32" customWidth="1"/>
+    <col min="10" max="10" width="52.453125" customWidth="1"/>
+    <col min="11" max="11" width="22.453125" customWidth="1"/>
+    <col min="12" max="12" width="52.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="33.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="73" t="s">
+    <row r="1" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B1" s="96" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="68" t="s">
+      <c r="C1" s="92" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="75" t="s">
+      <c r="D1" s="99" t="s">
         <v>31</v>
       </c>
       <c r="E1" s="4" t="s">
@@ -3939,1109 +3928,1139 @@
       <c r="F1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="77" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1" s="78"/>
-    </row>
-    <row r="2" spans="1:8" ht="46.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="74"/>
-      <c r="C2" s="51" t="s">
+      <c r="G1" s="101"/>
+      <c r="H1" s="102"/>
+    </row>
+    <row r="2" spans="1:8" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B2" s="97"/>
+      <c r="C2" s="93"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="40" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="41" t="s">
+        <v>124</v>
+      </c>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+    </row>
+    <row r="3" spans="1:8" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="98"/>
+      <c r="C3" s="53" t="s">
         <v>134</v>
       </c>
-      <c r="D2" s="76"/>
-      <c r="E2" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="40" t="s">
-        <v>124</v>
-      </c>
-      <c r="G2" s="67" t="s">
-        <v>35</v>
-      </c>
-      <c r="H2" s="67" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" s="23">
-        <f>SUM(B4:B5)/A3</f>
+      <c r="D3" s="100"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="41" t="s">
+        <v>71</v>
+      </c>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+    </row>
+    <row r="4" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="24">
+        <f>SUM(B5:B7)/A4</f>
         <v>1</v>
       </c>
-      <c r="C3" s="43"/>
-      <c r="D3" s="58">
-        <f>SUM(D4:D5)</f>
-        <v>2</v>
-      </c>
-      <c r="E3" s="37" t="s">
+      <c r="C4" s="45"/>
+      <c r="D4" s="60">
+        <f>SUM(D5:D7)</f>
+        <v>3</v>
+      </c>
+      <c r="E4" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="F3" s="38"/>
-      <c r="G3" s="79"/>
-      <c r="H3" s="80"/>
-    </row>
-    <row r="4" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4" s="19">
-        <f>D4</f>
-        <v>1</v>
-      </c>
-      <c r="C4" s="19"/>
-      <c r="D4" s="56">
-        <f>IF(F4="положительно",1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="F4" s="65" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="71"/>
-      <c r="H4" s="72"/>
-    </row>
-    <row r="5" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F4" s="39"/>
+      <c r="G4" s="103"/>
+      <c r="H4" s="104"/>
+    </row>
+    <row r="5" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1</v>
       </c>
-      <c r="B5" s="19">
+      <c r="B5" s="20">
         <f>D5</f>
         <v>1</v>
       </c>
-      <c r="C5" s="19"/>
-      <c r="D5" s="56">
-        <f>IF(OR(F5="положительно",F5="не требуется"),1,0)</f>
+      <c r="C5" s="20"/>
+      <c r="D5" s="58">
+        <f>IF(F5="положительно",1,0)</f>
         <v>1</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="77"/>
+      <c r="H5" s="78"/>
+    </row>
+    <row r="6" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6" s="20">
+        <f>D6</f>
+        <v>1</v>
+      </c>
+      <c r="C6" s="20"/>
+      <c r="D6" s="58">
+        <f>IF(OR(F6="положительно",F6="не требуется"),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="65" t="s">
+      <c r="F6" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="71"/>
-      <c r="H5" s="72"/>
-    </row>
-    <row r="6" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6">
+      <c r="G6" s="77"/>
+      <c r="H6" s="78"/>
+    </row>
+    <row r="7" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7" s="20">
+        <f>D7</f>
+        <v>1</v>
+      </c>
+      <c r="C7" s="20"/>
+      <c r="D7" s="58">
+        <f>IF(OR(F7="положительно",F7="не требуется"),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F7" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="68"/>
+      <c r="H7" s="69"/>
+    </row>
+    <row r="8" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8">
         <v>18</v>
       </c>
-      <c r="B6" s="21">
-        <f>SUM(B7:B12)/A6</f>
+      <c r="B8" s="22">
+        <f>SUM(B9:B14)/A8</f>
         <v>1</v>
       </c>
-      <c r="C6" s="44"/>
-      <c r="D6" s="54">
-        <f>SUM(D7:D12)</f>
+      <c r="C8" s="46"/>
+      <c r="D8" s="56">
+        <f>SUM(D9:D14)</f>
         <v>18</v>
       </c>
-      <c r="E6" s="30" t="s">
+      <c r="E8" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="16"/>
-      <c r="G6" s="81"/>
-      <c r="H6" s="82"/>
-    </row>
-    <row r="7" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7">
+      <c r="F8" s="16"/>
+      <c r="G8" s="81"/>
+      <c r="H8" s="82"/>
+    </row>
+    <row r="9" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9">
         <v>3</v>
       </c>
-      <c r="B7" s="19">
-        <f t="shared" ref="B7:B12" si="0">D7</f>
+      <c r="B9" s="20">
+        <f t="shared" ref="B9:B14" si="0">D9</f>
         <v>3</v>
       </c>
-      <c r="C7" s="19"/>
-      <c r="D7" s="56">
-        <f>IF(F7="положительно",3,IF(F7="сомнительно",2,0))</f>
+      <c r="C9" s="20"/>
+      <c r="D9" s="58">
+        <f>IF(F9="положительно",3,IF(F9="сомнительно",2,0))</f>
         <v>3</v>
       </c>
-      <c r="E7" s="41" t="s">
+      <c r="E9" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="65" t="s">
+      <c r="F9" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="71"/>
-      <c r="H7" s="72"/>
-    </row>
-    <row r="8" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8">
+      <c r="G9" s="77"/>
+      <c r="H9" s="78"/>
+    </row>
+    <row r="10" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10">
         <v>3</v>
       </c>
-      <c r="B8" s="19">
+      <c r="B10" s="20">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C8" s="19"/>
-      <c r="D8" s="56">
-        <f t="shared" ref="D8:D12" si="1">IF(F8="положительно",3,IF(F8="сомнительно",2,0))</f>
+      <c r="C10" s="20"/>
+      <c r="D10" s="58">
+        <f t="shared" ref="D10:D14" si="1">IF(F10="положительно",3,IF(F10="сомнительно",2,0))</f>
         <v>3</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="65" t="s">
+      <c r="F10" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="G8" s="71"/>
-      <c r="H8" s="72"/>
-    </row>
-    <row r="9" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9">
+      <c r="G10" s="77"/>
+      <c r="H10" s="78"/>
+    </row>
+    <row r="11" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11">
         <v>3</v>
       </c>
-      <c r="B9" s="19">
+      <c r="B11" s="20">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C9" s="19"/>
-      <c r="D9" s="56">
+      <c r="C11" s="20"/>
+      <c r="D11" s="58">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="65" t="s">
+      <c r="F11" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="71"/>
-      <c r="H9" s="72"/>
-    </row>
-    <row r="10" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10">
+      <c r="G11" s="77"/>
+      <c r="H11" s="78"/>
+    </row>
+    <row r="12" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12">
         <v>3</v>
       </c>
-      <c r="B10" s="19">
+      <c r="B12" s="20">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C10" s="19"/>
-      <c r="D10" s="56">
+      <c r="C12" s="20"/>
+      <c r="D12" s="58">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F10" s="65" t="s">
+      <c r="F12" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="G10" s="71"/>
-      <c r="H10" s="72"/>
-    </row>
-    <row r="11" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11">
+      <c r="G12" s="77"/>
+      <c r="H12" s="78"/>
+    </row>
+    <row r="13" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13">
         <v>3</v>
       </c>
-      <c r="B11" s="19">
+      <c r="B13" s="20">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="56">
-        <f>IF(OR(F11="положительно",F11="не требуется"),3,IF(F11="сомнительно",2,0))</f>
+      <c r="C13" s="20"/>
+      <c r="D13" s="58">
+        <f>IF(OR(F13="положительно",F13="не требуется"),3,IF(F13="сомнительно",2,0))</f>
         <v>3</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="65" t="s">
+      <c r="F13" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="G11" s="71"/>
-      <c r="H11" s="72"/>
-    </row>
-    <row r="12" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12">
+      <c r="G13" s="77"/>
+      <c r="H13" s="78"/>
+    </row>
+    <row r="14" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14">
         <v>3</v>
       </c>
-      <c r="B12" s="19">
+      <c r="B14" s="20">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="56">
+      <c r="C14" s="20"/>
+      <c r="D14" s="58">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F12" s="65" t="s">
+      <c r="F14" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="G12" s="71"/>
-      <c r="H12" s="72"/>
-    </row>
-    <row r="13" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13">
+      <c r="G14" s="77"/>
+      <c r="H14" s="78"/>
+    </row>
+    <row r="15" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15">
         <v>16</v>
       </c>
-      <c r="B13" s="23">
-        <f>SUM(B14:B15)/A13</f>
+      <c r="B15" s="24">
+        <f>SUM(B16:B17)/A15</f>
         <v>1</v>
       </c>
-      <c r="C13" s="45"/>
-      <c r="D13" s="55">
-        <f>SUM(D14:D15)</f>
+      <c r="C15" s="47"/>
+      <c r="D15" s="57">
+        <f>SUM(D16:D17)</f>
         <v>16</v>
       </c>
-      <c r="E13" s="31" t="s">
+      <c r="E15" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="F13" s="17"/>
-      <c r="G13" s="69"/>
-      <c r="H13" s="70"/>
-    </row>
-    <row r="14" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14">
+      <c r="F15" s="18"/>
+      <c r="G15" s="94"/>
+      <c r="H15" s="95"/>
+    </row>
+    <row r="16" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16">
         <v>8</v>
       </c>
-      <c r="B14" s="19">
-        <f>D14</f>
+      <c r="B16" s="20">
+        <f>D16</f>
         <v>8</v>
       </c>
-      <c r="C14" s="12" t="str">
-        <f>IF(F14="отрицательно","Х","О")</f>
+      <c r="C16" s="12" t="str">
+        <f>IF(F16="отрицательно","Х","О")</f>
         <v>О</v>
       </c>
-      <c r="D14" s="56">
-        <f>IF(OR(F14="положительно",F14="не требуется"),8,IF(F14="сомнительно",4,0))</f>
+      <c r="D16" s="58">
+        <f>IF(OR(F16="положительно",F16="не требуется"),8,IF(F16="сомнительно",4,0))</f>
         <v>8</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="65" t="s">
-        <v>137</v>
-      </c>
-      <c r="G14" s="71"/>
-      <c r="H14" s="72"/>
-    </row>
-    <row r="15" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15">
+      <c r="F16" s="61" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16" s="77"/>
+      <c r="H16" s="78"/>
+    </row>
+    <row r="17" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17">
         <v>8</v>
       </c>
-      <c r="B15" s="19">
-        <f>D15</f>
+      <c r="B17" s="20">
+        <f>D17</f>
         <v>8</v>
       </c>
-      <c r="C15" s="12" t="str">
-        <f>IF(F15="отрицательно","Х","О")</f>
+      <c r="C17" s="12" t="str">
+        <f>IF(F17="отрицательно","Х","О")</f>
         <v>О</v>
       </c>
-      <c r="D15" s="56">
-        <f>IF(OR(F15="положительно",F15="не требуется"),8,IF(F15="сомнительно",4,0))</f>
+      <c r="D17" s="58">
+        <f>IF(OR(F17="положительно",F17="не требуется"),8,IF(F17="сомнительно",4,0))</f>
         <v>8</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F15" s="65" t="s">
-        <v>137</v>
-      </c>
-      <c r="G15" s="71"/>
-      <c r="H15" s="72"/>
-    </row>
-    <row r="16" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16">
+      <c r="F17" s="61" t="s">
+        <v>20</v>
+      </c>
+      <c r="G17" s="77"/>
+      <c r="H17" s="78"/>
+    </row>
+    <row r="18" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18">
         <v>6</v>
       </c>
-      <c r="B16" s="23">
-        <f>B17/6</f>
+      <c r="B18" s="24">
+        <f>B19/6</f>
         <v>1</v>
       </c>
-      <c r="C16" s="45"/>
-      <c r="D16" s="54">
-        <f>D17</f>
+      <c r="C18" s="47"/>
+      <c r="D18" s="56">
+        <f>D19</f>
         <v>6</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E18" s="1" t="s">
         <v>1</v>
-      </c>
-      <c r="F16" s="16"/>
-      <c r="G16" s="81"/>
-      <c r="H16" s="82"/>
-    </row>
-    <row r="17" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>6</v>
-      </c>
-      <c r="B17" s="19">
-        <f>D17</f>
-        <v>6</v>
-      </c>
-      <c r="C17" s="19"/>
-      <c r="D17" s="56">
-        <f>IF(OR(F17="положительно",F17="не требуется"),6,IF(F17="сомнительно",3,0))</f>
-        <v>6</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F17" s="65" t="s">
-        <v>20</v>
-      </c>
-      <c r="G17" s="84"/>
-      <c r="H17" s="85"/>
-    </row>
-    <row r="18" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <f>SUM(A19:A21)</f>
-        <v>24</v>
-      </c>
-      <c r="B18" s="23">
-        <f>SUM(B19:B21)/A18</f>
-        <v>1</v>
-      </c>
-      <c r="C18" s="46"/>
-      <c r="D18" s="54">
-        <f>SUM(D19:D21)</f>
-        <v>24</v>
-      </c>
-      <c r="E18" s="22" t="s">
-        <v>3</v>
       </c>
       <c r="F18" s="16"/>
       <c r="G18" s="81"/>
       <c r="H18" s="82"/>
     </row>
-    <row r="19" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>8</v>
-      </c>
-      <c r="B19" s="19">
+        <v>6</v>
+      </c>
+      <c r="B19" s="20">
         <f>D19</f>
-        <v>8</v>
-      </c>
-      <c r="C19" s="12" t="str">
-        <f>IF(F19="отрицательно","Х","О")</f>
-        <v>О</v>
-      </c>
-      <c r="D19" s="56">
-        <f>IF(OR(F19="положительно",F19="не требуется"),8,IF(F19="сомнительно",4,0))</f>
-        <v>8</v>
+        <v>6</v>
+      </c>
+      <c r="C19" s="20"/>
+      <c r="D19" s="58">
+        <f>IF(OR(F19="положительно",F19="не требуется"),6,IF(F19="сомнительно",3,0))</f>
+        <v>6</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="F19" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="G19" s="71"/>
-      <c r="H19" s="72"/>
-    </row>
-    <row r="20" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G19" s="90"/>
+      <c r="H19" s="91"/>
+    </row>
+    <row r="20" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>8</v>
-      </c>
-      <c r="B20" s="19">
-        <f>D20</f>
-        <v>8</v>
-      </c>
-      <c r="C20" s="12" t="str">
-        <f t="shared" ref="C20:C21" si="2">IF(F20="отрицательно","Х","О")</f>
-        <v>О</v>
-      </c>
+        <f>SUM(A21:A23)</f>
+        <v>24</v>
+      </c>
+      <c r="B20" s="24">
+        <f>SUM(B21:B23)/A20</f>
+        <v>1</v>
+      </c>
+      <c r="C20" s="48"/>
       <c r="D20" s="56">
-        <f>IF(OR(F20="положительно",F20="не требуется"),8,IF(F20="сомнительно",4,0))</f>
-        <v>8</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F20" s="65" t="s">
-        <v>20</v>
-      </c>
-      <c r="G20" s="71"/>
-      <c r="H20" s="72"/>
-    </row>
-    <row r="21" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+        <f>SUM(D21:D23)</f>
+        <v>24</v>
+      </c>
+      <c r="E20" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="16"/>
+      <c r="G20" s="81"/>
+      <c r="H20" s="82"/>
+    </row>
+    <row r="21" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>8</v>
       </c>
-      <c r="B21" s="19">
+      <c r="B21" s="20">
         <f>D21</f>
         <v>8</v>
       </c>
       <c r="C21" s="12" t="str">
+        <f>IF(F21="отрицательно","Х","О")</f>
+        <v>О</v>
+      </c>
+      <c r="D21" s="58">
+        <f>IF(OR(F21="положительно",F21="не требуется"),8,IF(F21="сомнительно",4,0))</f>
+        <v>8</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F21" s="61" t="s">
+        <v>20</v>
+      </c>
+      <c r="G21" s="77"/>
+      <c r="H21" s="78"/>
+    </row>
+    <row r="22" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>8</v>
+      </c>
+      <c r="B22" s="20">
+        <f>D22</f>
+        <v>8</v>
+      </c>
+      <c r="C22" s="12" t="str">
+        <f t="shared" ref="C22:C23" si="2">IF(F22="отрицательно","Х","О")</f>
+        <v>О</v>
+      </c>
+      <c r="D22" s="58">
+        <f>IF(OR(F22="положительно",F22="не требуется"),8,IF(F22="сомнительно",4,0))</f>
+        <v>8</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F22" s="61" t="s">
+        <v>137</v>
+      </c>
+      <c r="G22" s="77"/>
+      <c r="H22" s="78"/>
+    </row>
+    <row r="23" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>8</v>
+      </c>
+      <c r="B23" s="20">
+        <f>D23</f>
+        <v>8</v>
+      </c>
+      <c r="C23" s="12" t="str">
         <f t="shared" si="2"/>
         <v>О</v>
       </c>
-      <c r="D21" s="56">
-        <f>IF(OR(F21="положительно",F21="не требуется"),8,IF(F21="сомнительно",4,0))</f>
+      <c r="D23" s="58">
+        <f>IF(OR(F23="положительно",F23="не требуется"),8,IF(F23="сомнительно",4,0))</f>
         <v>8</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="F21" s="65" t="s">
+      <c r="F23" s="61" t="s">
         <v>137</v>
       </c>
-      <c r="G21" s="71"/>
-      <c r="H21" s="72"/>
-    </row>
-    <row r="22" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22">
+      <c r="G23" s="77"/>
+      <c r="H23" s="78"/>
+    </row>
+    <row r="24" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24">
         <v>8</v>
       </c>
-      <c r="B22" s="32">
-        <f>SUM(B23:B24)/A22</f>
+      <c r="B24" s="33">
+        <f>SUM(B25:B26)/A24</f>
         <v>1</v>
       </c>
-      <c r="C22" s="50"/>
-      <c r="D22" s="54">
-        <f>SUM(D23:D24)</f>
+      <c r="C24" s="52"/>
+      <c r="D24" s="56">
+        <f>SUM(D25:D26)</f>
         <v>8</v>
       </c>
-      <c r="E22" s="48" t="s">
+      <c r="E24" s="50" t="s">
         <v>54</v>
       </c>
-      <c r="F22" s="48"/>
-      <c r="G22" s="49"/>
-      <c r="H22" s="49"/>
-    </row>
-    <row r="23" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23">
+      <c r="F24" s="50"/>
+      <c r="G24" s="51"/>
+      <c r="H24" s="51"/>
+    </row>
+    <row r="25" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25">
         <v>6</v>
       </c>
-      <c r="B23" s="19">
-        <f>D23</f>
+      <c r="B25" s="20">
+        <f>D25</f>
         <v>6</v>
       </c>
-      <c r="C23" s="12" t="str">
-        <f>IF(F23="отрицательно","Х","О")</f>
+      <c r="C25" s="12" t="str">
+        <f>IF(F25="отрицательно","Х","О")</f>
         <v>О</v>
       </c>
-      <c r="D23" s="56">
-        <f t="shared" ref="D23" si="3">IF(OR(F23="положительно",F23="не требуется"),6,IF(F23="сомнительно",3,0))</f>
+      <c r="D25" s="58">
+        <f t="shared" ref="D25" si="3">IF(OR(F25="положительно",F25="не требуется"),6,IF(F25="сомнительно",3,0))</f>
         <v>6</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E25" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F23" s="65" t="s">
-        <v>137</v>
-      </c>
-      <c r="G23" s="71"/>
-      <c r="H23" s="72"/>
-    </row>
-    <row r="24" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24">
+      <c r="F25" s="61" t="s">
+        <v>20</v>
+      </c>
+      <c r="G25" s="77"/>
+      <c r="H25" s="78"/>
+    </row>
+    <row r="26" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26">
         <v>2</v>
       </c>
-      <c r="B24" s="19">
-        <f>D24</f>
+      <c r="B26" s="20">
+        <f>D26</f>
         <v>2</v>
       </c>
-      <c r="C24" s="19"/>
-      <c r="D24" s="56">
-        <f>IF(F24="положительно",2,IF(F24="сомнительно",1,0))</f>
+      <c r="C26" s="20"/>
+      <c r="D26" s="58">
+        <f>IF(F26="положительно",2,IF(F26="сомнительно",1,0))</f>
         <v>2</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E26" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="F24" s="65" t="s">
+      <c r="F26" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="G24" s="71"/>
-      <c r="H24" s="72"/>
-    </row>
-    <row r="25" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25">
+      <c r="G26" s="77"/>
+      <c r="H26" s="78"/>
+    </row>
+    <row r="27" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27">
         <v>16</v>
       </c>
-      <c r="B25" s="23">
-        <f>SUM(B26:B29)/A25</f>
+      <c r="B27" s="24">
+        <f>SUM(B28:B31)/A27</f>
         <v>1</v>
       </c>
-      <c r="C25" s="45"/>
-      <c r="D25" s="54">
-        <f>SUM(D26:D29)</f>
+      <c r="C27" s="47"/>
+      <c r="D27" s="56">
+        <f>SUM(D28:D31)</f>
         <v>16</v>
       </c>
-      <c r="E25" s="20" t="s">
+      <c r="E27" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="F25" s="30"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20"/>
-    </row>
-    <row r="26" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="19">
-        <f t="shared" ref="B26:B29" si="4">D26</f>
+      <c r="F27" s="31"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="21"/>
+    </row>
+    <row r="28" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B28" s="20">
+        <f t="shared" ref="B28:B31" si="4">D28</f>
         <v>4</v>
       </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="56">
-        <f>IF(OR(F26="положительно",F26="не требуется"),4,IF(F26="сомнительно",2,0))</f>
+      <c r="C28" s="20"/>
+      <c r="D28" s="58">
+        <f>IF(OR(F28="положительно",F28="не требуется"),4,IF(F28="сомнительно",2,0))</f>
         <v>4</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E28" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="F26" s="65" t="s">
-        <v>137</v>
-      </c>
-      <c r="G26" s="71"/>
-      <c r="H26" s="72"/>
-    </row>
-    <row r="27" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="19">
+      <c r="F28" s="61" t="s">
+        <v>20</v>
+      </c>
+      <c r="G28" s="77"/>
+      <c r="H28" s="78"/>
+    </row>
+    <row r="29" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B29" s="20">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="C27" s="19"/>
-      <c r="D27" s="56">
-        <f>IF(OR(F27="положительно",F27="не требуется"),4,IF(F27="сомнительно",2,0))</f>
+      <c r="C29" s="20"/>
+      <c r="D29" s="58">
+        <f>IF(OR(F29="положительно",F29="не требуется"),4,IF(F29="сомнительно",2,0))</f>
         <v>4</v>
       </c>
-      <c r="E27" s="42" t="s">
+      <c r="E29" s="43" t="s">
         <v>131</v>
       </c>
-      <c r="F27" s="65" t="s">
-        <v>137</v>
-      </c>
-      <c r="G27" s="71"/>
-      <c r="H27" s="72"/>
-    </row>
-    <row r="28" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="19">
+      <c r="F29" s="61" t="s">
+        <v>20</v>
+      </c>
+      <c r="G29" s="77"/>
+      <c r="H29" s="78"/>
+    </row>
+    <row r="30" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="20">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="C28" s="19"/>
-      <c r="D28" s="56">
-        <f>IF(OR(F28="положительно",F28="не требуется"),4,IF(F28="сомнительно",2,0))</f>
+      <c r="C30" s="20"/>
+      <c r="D30" s="58">
+        <f>IF(OR(F30="положительно",F30="не требуется"),4,IF(F30="сомнительно",2,0))</f>
         <v>4</v>
       </c>
-      <c r="E28" s="42" t="s">
+      <c r="E30" s="43" t="s">
         <v>132</v>
       </c>
-      <c r="F28" s="65" t="s">
-        <v>137</v>
-      </c>
-      <c r="G28" s="71"/>
-      <c r="H28" s="72"/>
-    </row>
-    <row r="29" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="19">
+      <c r="F30" s="61" t="s">
+        <v>20</v>
+      </c>
+      <c r="G30" s="77"/>
+      <c r="H30" s="78"/>
+    </row>
+    <row r="31" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B31" s="20">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="C29" s="19"/>
-      <c r="D29" s="56">
-        <f>IF(OR(F29="положительно",F29="не требуется"),4,IF(F29="сомнительно",2,0))</f>
+      <c r="C31" s="20"/>
+      <c r="D31" s="58">
+        <f>IF(OR(F31="положительно",F31="не требуется"),4,IF(F31="сомнительно",2,0))</f>
         <v>4</v>
       </c>
-      <c r="E29" s="42" t="s">
+      <c r="E31" s="43" t="s">
         <v>133</v>
       </c>
-      <c r="F29" s="65" t="s">
-        <v>137</v>
-      </c>
-      <c r="G29" s="71"/>
-      <c r="H29" s="72"/>
-    </row>
-    <row r="30" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="32" t="str">
-        <f>IF(OR(D32=0),0,IF(OR(D31=100),1,IF(OR(D32=""),"",IF(OR(D31=""),""))))</f>
+      <c r="F31" s="61" t="s">
+        <v>20</v>
+      </c>
+      <c r="G31" s="77"/>
+      <c r="H31" s="78"/>
+    </row>
+    <row r="32" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B32" s="33" t="str">
+        <f>IF(OR(D34=0),0,IF(OR(D33=100),1,IF(OR(D34=""),"",IF(OR(D33=""),""))))</f>
         <v/>
       </c>
-      <c r="C30" s="47"/>
-      <c r="D30" s="47"/>
-      <c r="E30" s="30" t="s">
+      <c r="C32" s="49"/>
+      <c r="D32" s="49"/>
+      <c r="E32" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="F30" s="16"/>
-      <c r="G30" s="81"/>
-      <c r="H30" s="82"/>
-      <c r="L30" s="83"/>
-      <c r="M30" s="83"/>
-      <c r="N30" s="83"/>
-      <c r="O30" s="83"/>
-      <c r="P30" s="29"/>
-      <c r="Q30" s="83"/>
-      <c r="R30" s="83"/>
-    </row>
-    <row r="31" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="15"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="56" t="str">
-        <f>IF(F31="Обнаружено",100,"")</f>
+      <c r="F32" s="16"/>
+      <c r="G32" s="81"/>
+      <c r="H32" s="82"/>
+      <c r="L32" s="89"/>
+      <c r="M32" s="89"/>
+      <c r="N32" s="89"/>
+      <c r="O32" s="89"/>
+      <c r="P32" s="30"/>
+      <c r="Q32" s="89"/>
+      <c r="R32" s="89"/>
+    </row>
+    <row r="33" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B33" s="15"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="58" t="str">
+        <f>IF(F33="Обнаружено",100,"")</f>
         <v/>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="E33" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F31" s="65" t="s">
+      <c r="F33" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="G31" s="71"/>
-      <c r="H31" s="72"/>
-    </row>
-    <row r="32" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="59"/>
-      <c r="C32" s="60" t="str">
-        <f>IF(F32="Обнаружено","КО","ОК")</f>
+      <c r="G33" s="83"/>
+      <c r="H33" s="83"/>
+    </row>
+    <row r="34" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B34" s="62"/>
+      <c r="C34" s="63" t="str">
+        <f>IF(F34="Обнаружено","КО","ОК")</f>
         <v>ОК</v>
       </c>
-      <c r="D32" s="61" t="str">
-        <f>IF(F32="обнаружено",0,"")</f>
+      <c r="D34" s="64" t="str">
+        <f>IF(F34="обнаружено",0,"")</f>
         <v/>
       </c>
-      <c r="E32" s="62" t="s">
+      <c r="E34" s="65" t="s">
         <v>59</v>
       </c>
-      <c r="F32" s="63" t="s">
+      <c r="F34" s="66" t="s">
         <v>33</v>
       </c>
-      <c r="G32" s="86"/>
-      <c r="H32" s="87"/>
-    </row>
-    <row r="33" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="3"/>
-      <c r="C33" s="12" t="str">
-        <f>IF(F33="Обнаружено","✔","")</f>
+      <c r="G34" s="84"/>
+      <c r="H34" s="85"/>
+    </row>
+    <row r="35" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B35" s="3"/>
+      <c r="C35" s="12" t="str">
+        <f>IF(F35="Обнаружено","✔","")</f>
         <v/>
       </c>
-      <c r="D33" s="56"/>
-      <c r="E33" s="2" t="s">
+      <c r="D35" s="58"/>
+      <c r="E35" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="F33" s="65" t="s">
+      <c r="F35" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="G33" s="86"/>
-      <c r="H33" s="87"/>
-    </row>
-    <row r="34" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="32">
-        <f>IF(OR(D35=0,D36=0,D37=0,D38=0),0,100%)</f>
+      <c r="G35" s="86"/>
+      <c r="H35" s="87"/>
+    </row>
+    <row r="36" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B36" s="33">
+        <f>IF(OR(D37=0,D38=0,D39=0,D40=0),0,100%)</f>
         <v>1</v>
       </c>
-      <c r="C34" s="47"/>
-      <c r="D34" s="57"/>
-      <c r="E34" s="30" t="s">
+      <c r="C36" s="49"/>
+      <c r="D36" s="59"/>
+      <c r="E36" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="F34" s="16"/>
-      <c r="G34" s="81"/>
-      <c r="H34" s="82"/>
-    </row>
-    <row r="35" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="10" t="str">
-        <f>D35</f>
-        <v/>
-      </c>
-      <c r="C35" s="12" t="str">
-        <f>IF(F35="Обнаружено","КО","ОК")</f>
-        <v>ОК</v>
-      </c>
-      <c r="D35" s="56" t="str">
-        <f>IF(F35="обнаружено",0,"")</f>
-        <v/>
-      </c>
-      <c r="E35" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="F35" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="G35" s="71"/>
-      <c r="H35" s="72"/>
-    </row>
-    <row r="36" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="10" t="str">
-        <f>D36</f>
-        <v/>
-      </c>
-      <c r="C36" s="12" t="str">
-        <f t="shared" ref="C36:C38" si="5">IF(F36="Обнаружено","КО","ОК")</f>
-        <v>ОК</v>
-      </c>
-      <c r="D36" s="56" t="str">
-        <f>IF(F36="обнаружено",0,"")</f>
-        <v/>
-      </c>
-      <c r="E36" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="F36" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="G36" s="71"/>
-      <c r="H36" s="72"/>
-    </row>
-    <row r="37" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F36" s="16"/>
+      <c r="G36" s="81"/>
+      <c r="H36" s="82"/>
+    </row>
+    <row r="37" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B37" s="10" t="str">
         <f>D37</f>
         <v/>
       </c>
       <c r="C37" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(F37="Обнаружено","КО","ОК")</f>
         <v>ОК</v>
       </c>
-      <c r="D37" s="56" t="str">
+      <c r="D37" s="58" t="str">
         <f>IF(F37="обнаружено",0,"")</f>
         <v/>
       </c>
       <c r="E37" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="F37" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="F37" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="G37" s="71"/>
-      <c r="H37" s="72"/>
-    </row>
-    <row r="38" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G37" s="77"/>
+      <c r="H37" s="78"/>
+    </row>
+    <row r="38" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B38" s="10" t="str">
         <f>D38</f>
         <v/>
       </c>
       <c r="C38" s="12" t="str">
+        <f t="shared" ref="C38:C40" si="5">IF(F38="Обнаружено","КО","ОК")</f>
+        <v>ОК</v>
+      </c>
+      <c r="D38" s="58" t="str">
+        <f>IF(F38="обнаружено",0,"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F38" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="G38" s="77"/>
+      <c r="H38" s="78"/>
+    </row>
+    <row r="39" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B39" s="10" t="str">
+        <f>D39</f>
+        <v/>
+      </c>
+      <c r="C39" s="12" t="str">
         <f t="shared" si="5"/>
         <v>ОК</v>
       </c>
-      <c r="D38" s="56" t="str">
-        <f>IF(F38="обнаружено",0,"")</f>
+      <c r="D39" s="58" t="str">
+        <f>IF(F39="обнаружено",0,"")</f>
         <v/>
       </c>
-      <c r="E38" s="11" t="s">
+      <c r="E39" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F39" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="G39" s="77"/>
+      <c r="H39" s="78"/>
+    </row>
+    <row r="40" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B40" s="10" t="str">
+        <f>D40</f>
+        <v/>
+      </c>
+      <c r="C40" s="12" t="str">
+        <f t="shared" si="5"/>
+        <v>ОК</v>
+      </c>
+      <c r="D40" s="58" t="str">
+        <f>IF(F40="обнаружено",0,"")</f>
+        <v/>
+      </c>
+      <c r="E40" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="F38" s="26" t="s">
+      <c r="F40" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="G38" s="71"/>
-      <c r="H38" s="72"/>
-    </row>
-    <row r="39" spans="2:8" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="92" t="s">
+      <c r="G40" s="77"/>
+      <c r="H40" s="78"/>
+    </row>
+    <row r="41" spans="2:8" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B41" s="75" t="s">
         <v>49</v>
       </c>
-      <c r="C39" s="93"/>
-      <c r="D39" s="66">
-        <f>IF(OR(D35=0,D36=0,D37=0,D38=0,D32=0),0,IF(D31=100,1,SUM(D3,D6,D16,D18,D13,D22,D25)/90))</f>
+      <c r="C41" s="75"/>
+      <c r="D41" s="71">
+        <f>IF(OR(D37=0,D38=0,D39=0,D40=0,D34=0),0,IF(D33=100,1,SUM(D4,D8,D18,D20,D15,D24,D27)/91))</f>
         <v>1</v>
       </c>
-      <c r="E39" s="9"/>
-      <c r="F39" s="14" t="s">
+      <c r="E41" s="9"/>
+      <c r="F41" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="G39" s="96"/>
-      <c r="H39" s="97"/>
-    </row>
-    <row r="40" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="94"/>
-      <c r="C40" s="95"/>
-      <c r="D40" s="64" t="str">
-        <f>IF(D39&lt;=82%,"недопустимо",IF(D39&gt;=96%,"отлично",IF(D39&gt;=93%,"хорошо","неприемлемо")))</f>
+      <c r="G41" s="79"/>
+      <c r="H41" s="80"/>
+    </row>
+    <row r="42" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B42" s="76"/>
+      <c r="C42" s="76"/>
+      <c r="D42" s="67" t="str">
+        <f>IF(D41&lt;=82%,"недопустимо",IF(D41&gt;=96%,"отлично",IF(D41&gt;=93%,"хорошо","неприемлемо")))</f>
         <v>отлично</v>
-      </c>
-      <c r="E40" s="9"/>
-      <c r="F40" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="G40" s="90"/>
-      <c r="H40" s="91"/>
-    </row>
-    <row r="41" spans="2:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="88"/>
-      <c r="C41" s="89"/>
-      <c r="D41" s="52"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="G41" s="90"/>
-      <c r="H41" s="91"/>
-    </row>
-    <row r="42" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="88" t="s">
-        <v>139</v>
-      </c>
-      <c r="C42" s="89"/>
-      <c r="D42" s="53">
-        <f>COUNTIF(F14:F15,"отрицательно")+COUNTIF(F19:F21,"отрицательно")+COUNTIF(F23,"отрицательно")+COUNTIF(F35:F38,"обнаружено")</f>
-        <v>0</v>
       </c>
       <c r="E42" s="9"/>
       <c r="F42" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="G42" s="73"/>
+      <c r="H42" s="74"/>
+    </row>
+    <row r="43" spans="2:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B43" s="72"/>
+      <c r="C43" s="72"/>
+      <c r="D43" s="54"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="G43" s="73"/>
+      <c r="H43" s="74"/>
+    </row>
+    <row r="44" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B44" s="72" t="s">
+        <v>139</v>
+      </c>
+      <c r="C44" s="72"/>
+      <c r="D44" s="55">
+        <f>COUNTIF(F16:F17,"отрицательно")+COUNTIF(F21:F23,"отрицательно")+COUNTIF(F25,"отрицательно")+COUNTIF(F37:F40,"обнаружено")</f>
+        <v>0</v>
+      </c>
+      <c r="E44" s="9"/>
+      <c r="F44" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="G42" s="90"/>
-      <c r="H42" s="91"/>
-    </row>
-    <row r="43" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="88" t="s">
+      <c r="G44" s="73"/>
+      <c r="H44" s="74"/>
+    </row>
+    <row r="45" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B45" s="72" t="s">
         <v>140</v>
       </c>
-      <c r="C43" s="89"/>
-      <c r="D43" s="53">
-        <f>COUNTIF(F4:F5,"отрицательно")+COUNTIF(F4:F5,"сомнительно")+COUNTIF(F7:F12,"отрицательно")+COUNTIF(F7:F12,"сомнительно")+COUNTIF(F17,"сомнительно")+COUNTIF(F17,"отрицательно")+COUNTIF(F14:F15,"сомнительно")+COUNTIF(F19:F21,"сомнительно")+COUNTIF(F23,"сомнительно")+COUNTIF(F24,"сомнительно")+COUNTIF(F24,"отрицательно")+COUNTIF(F26:F29,"отрицательно")+COUNTIF(F26:F29,"сомнительно")</f>
+      <c r="C45" s="72"/>
+      <c r="D45" s="55">
+        <f>COUNTIF(F5:F6,"отрицательно")+COUNTIF(F5:F6,"сомнительно")+COUNTIF(F9:F14,"отрицательно")+COUNTIF(F9:F14,"сомнительно")+COUNTIF(F19,"сомнительно")+COUNTIF(F19,"отрицательно")+COUNTIF(F16:F17,"сомнительно")+COUNTIF(F21:F23,"сомнительно")+COUNTIF(F25,"сомнительно")+COUNTIF(F26,"сомнительно")+COUNTIF(F26,"отрицательно")+COUNTIF(F28:F31,"отрицательно")+COUNTIF(F28:F31,"сомнительно")</f>
         <v>0</v>
       </c>
-      <c r="E43" s="9"/>
-      <c r="F43" s="18" t="s">
+      <c r="E45" s="9"/>
+      <c r="F45" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="G43" s="27"/>
-      <c r="H43" s="28"/>
-    </row>
-    <row r="44" spans="2:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="88" t="s">
+      <c r="G45" s="28"/>
+      <c r="H45" s="29"/>
+    </row>
+    <row r="46" spans="2:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B46" s="72" t="s">
         <v>135</v>
       </c>
-      <c r="C44" s="89"/>
-      <c r="D44" s="53">
-        <f>IF(OR(F35="обнаружено",F36="обнаружено",F37="обнаружено",F38="обнаружено"),COUNTIF($F$35:$F$38,"обнаружено"),0)</f>
+      <c r="C46" s="72"/>
+      <c r="D46" s="55">
+        <f>IF(OR(F37="обнаружено",F38="обнаружено",F39="обнаружено",F40="обнаружено"),COUNTIF($F$37:$F$40,"обнаружено"),0)</f>
         <v>0</v>
       </c>
-      <c r="E44" s="9"/>
-      <c r="F44" s="18" t="s">
+      <c r="E46" s="9"/>
+      <c r="F46" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="G44" s="90"/>
-      <c r="H44" s="91"/>
-    </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B46" s="24"/>
-      <c r="C46" s="24"/>
-      <c r="D46" s="24"/>
-    </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="G46" s="73"/>
+      <c r="H46" s="74"/>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B48" s="25"/>
       <c r="C48" s="25"/>
       <c r="D48" s="25"/>
     </row>
+    <row r="50" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B50" s="26"/>
+      <c r="C50" s="26"/>
+      <c r="D50" s="26"/>
+    </row>
   </sheetData>
-  <mergeCells count="49">
+  <mergeCells count="52">
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="Q32:R32"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="L32:O32"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="B41:C42"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="G31:H31"/>
     <mergeCell ref="B44:C44"/>
-    <mergeCell ref="G44:H44"/>
-    <mergeCell ref="B39:C40"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="G40:H40"/>
     <mergeCell ref="G41:H41"/>
     <mergeCell ref="G42:H42"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="B43:C43"/>
     <mergeCell ref="G37:H37"/>
     <mergeCell ref="G38:H38"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="Q30:R30"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="L30:O30"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G39:H39"/>
   </mergeCells>
-  <conditionalFormatting sqref="F24 F30:F38 F4:F5">
+  <conditionalFormatting sqref="F26 F32:F40 F5:F7">
     <cfRule type="containsText" dxfId="36" priority="95" operator="containsText" text="отрицательно">
-      <formula>NOT(ISERROR(SEARCH("отрицательно",F4)))</formula>
+      <formula>NOT(ISERROR(SEARCH("отрицательно",F5)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F7:F12">
+  <conditionalFormatting sqref="F9:F14">
     <cfRule type="containsText" dxfId="35" priority="94" operator="containsText" text="отрицательно">
-      <formula>NOT(ISERROR(SEARCH("отрицательно",F7)))</formula>
+      <formula>NOT(ISERROR(SEARCH("отрицательно",F9)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F24 F16 F30:F38 F4:F12 F18">
+  <conditionalFormatting sqref="F26 F18 F32:F40 F20 F5:F14">
     <cfRule type="containsText" dxfId="34" priority="89" operator="containsText" text="сомнительно">
-      <formula>NOT(ISERROR(SEARCH("сомнительно",F4)))</formula>
+      <formula>NOT(ISERROR(SEARCH("сомнительно",F5)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F35:F38">
+  <conditionalFormatting sqref="F37:F40">
     <cfRule type="containsText" dxfId="33" priority="88" operator="containsText" text="не">
-      <formula>NOT(ISERROR(SEARCH("не",F35)))</formula>
+      <formula>NOT(ISERROR(SEARCH("не",F37)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D40">
+  <conditionalFormatting sqref="D42">
     <cfRule type="containsText" dxfId="32" priority="81" operator="containsText" text="отлично">
-      <formula>NOT(ISERROR(SEARCH("отлично",D40)))</formula>
+      <formula>NOT(ISERROR(SEARCH("отлично",D42)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="31" priority="83" operator="containsText" text="неприемлемо">
-      <formula>NOT(ISERROR(SEARCH("неприемлемо",D40)))</formula>
+      <formula>NOT(ISERROR(SEARCH("неприемлемо",D42)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="30" priority="84" operator="containsText" text="недопустимо">
-      <formula>NOT(ISERROR(SEARCH("недопустимо",D40)))</formula>
+      <formula>NOT(ISERROR(SEARCH("недопустимо",D42)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C35:C38">
+  <conditionalFormatting sqref="C37:C40">
     <cfRule type="containsText" dxfId="29" priority="49" operator="containsText" text="ОК">
-      <formula>NOT(ISERROR(SEARCH("ОК",C35)))</formula>
+      <formula>NOT(ISERROR(SEARCH("ОК",C37)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="28" priority="50" operator="containsText" text="ОК">
-      <formula>NOT(ISERROR(SEARCH("ОК",C35)))</formula>
+      <formula>NOT(ISERROR(SEARCH("ОК",C37)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="27" priority="185" operator="containsText" text="Х">
       <formula>NOT(ISERROR(SEARCH("Х",#REF!)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C35:C38">
+  <conditionalFormatting sqref="C37:C40">
     <cfRule type="containsText" dxfId="26" priority="57" operator="containsText" text="Х">
-      <formula>NOT(ISERROR(SEARCH("Х",C35)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Х",C37)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="25" priority="58" operator="containsText" text="О">
-      <formula>NOT(ISERROR(SEARCH("О",C35)))</formula>
+      <formula>NOT(ISERROR(SEARCH("О",C37)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C32:C38">
+  <conditionalFormatting sqref="C34:C40">
     <cfRule type="containsText" dxfId="24" priority="44" operator="containsText" text="ОК">
-      <formula>NOT(ISERROR(SEARCH("ОК",C32)))</formula>
+      <formula>NOT(ISERROR(SEARCH("ОК",C34)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="23" priority="45" operator="containsText" text="ОК">
-      <formula>NOT(ISERROR(SEARCH("ОК",C32)))</formula>
+      <formula>NOT(ISERROR(SEARCH("ОК",C34)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="22" priority="48" operator="containsText" text="Х">
       <formula>NOT(ISERROR(SEARCH("Х",#REF!)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C32:C38">
+  <conditionalFormatting sqref="C34:C40">
     <cfRule type="containsText" dxfId="21" priority="46" operator="containsText" text="Х">
-      <formula>NOT(ISERROR(SEARCH("Х",C32)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Х",C34)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="20" priority="47" operator="containsText" text="О">
-      <formula>NOT(ISERROR(SEARCH("О",C32)))</formula>
+      <formula>NOT(ISERROR(SEARCH("О",C34)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C33:C38">
+  <conditionalFormatting sqref="C35:C40">
     <cfRule type="containsText" dxfId="19" priority="30" operator="containsText" text="✔">
-      <formula>NOT(ISERROR(SEARCH("✔",C33)))</formula>
+      <formula>NOT(ISERROR(SEARCH("✔",C35)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F13:F15">
+  <conditionalFormatting sqref="F15:F17">
     <cfRule type="containsText" dxfId="18" priority="29" operator="containsText" text="отрицательно">
-      <formula>NOT(ISERROR(SEARCH("отрицательно",F13)))</formula>
+      <formula>NOT(ISERROR(SEARCH("отрицательно",F15)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F14:F15">
+  <conditionalFormatting sqref="F16:F17">
     <cfRule type="containsText" dxfId="17" priority="28" operator="containsText" text="отрицательно">
-      <formula>NOT(ISERROR(SEARCH("отрицательно",F14)))</formula>
+      <formula>NOT(ISERROR(SEARCH("отрицательно",F16)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F13:F15">
+  <conditionalFormatting sqref="F15:F17">
     <cfRule type="containsText" dxfId="16" priority="27" operator="containsText" text="сомнительно">
-      <formula>NOT(ISERROR(SEARCH("сомнительно",F13)))</formula>
+      <formula>NOT(ISERROR(SEARCH("сомнительно",F15)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F26:F29">
+  <conditionalFormatting sqref="F28:F31">
     <cfRule type="containsText" dxfId="15" priority="11" operator="containsText" text="отрицательно">
-      <formula>NOT(ISERROR(SEARCH("отрицательно",F26)))</formula>
+      <formula>NOT(ISERROR(SEARCH("отрицательно",F28)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F26:F29">
+  <conditionalFormatting sqref="F28:F31">
     <cfRule type="containsText" dxfId="14" priority="10" operator="containsText" text="сомнительно">
-      <formula>NOT(ISERROR(SEARCH("сомнительно",F26)))</formula>
+      <formula>NOT(ISERROR(SEARCH("сомнительно",F28)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F17">
+  <conditionalFormatting sqref="F19">
     <cfRule type="containsText" dxfId="13" priority="24" operator="containsText" text="отрицательно">
-      <formula>NOT(ISERROR(SEARCH("отрицательно",F17)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F17">
-    <cfRule type="containsText" dxfId="12" priority="23" operator="containsText" text="отрицательно">
-      <formula>NOT(ISERROR(SEARCH("отрицательно",F17)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F17">
-    <cfRule type="containsText" dxfId="11" priority="22" operator="containsText" text="сомнительно">
-      <formula>NOT(ISERROR(SEARCH("сомнительно",F17)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F26:F29">
-    <cfRule type="containsText" dxfId="10" priority="12" operator="containsText" text="отрицательно">
-      <formula>NOT(ISERROR(SEARCH("отрицательно",F26)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F19:F21">
-    <cfRule type="containsText" dxfId="9" priority="18" operator="containsText" text="отрицательно">
       <formula>NOT(ISERROR(SEARCH("отрицательно",F19)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F19:F21">
-    <cfRule type="containsText" dxfId="8" priority="17" operator="containsText" text="отрицательно">
+  <conditionalFormatting sqref="F19">
+    <cfRule type="containsText" dxfId="12" priority="23" operator="containsText" text="отрицательно">
       <formula>NOT(ISERROR(SEARCH("отрицательно",F19)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F19:F21">
-    <cfRule type="containsText" dxfId="7" priority="16" operator="containsText" text="сомнительно">
+  <conditionalFormatting sqref="F19">
+    <cfRule type="containsText" dxfId="11" priority="22" operator="containsText" text="сомнительно">
       <formula>NOT(ISERROR(SEARCH("сомнительно",F19)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F23">
-    <cfRule type="containsText" dxfId="6" priority="15" operator="containsText" text="отрицательно">
-      <formula>NOT(ISERROR(SEARCH("отрицательно",F23)))</formula>
+  <conditionalFormatting sqref="F28:F31">
+    <cfRule type="containsText" dxfId="10" priority="12" operator="containsText" text="отрицательно">
+      <formula>NOT(ISERROR(SEARCH("отрицательно",F28)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F23">
-    <cfRule type="containsText" dxfId="5" priority="14" operator="containsText" text="отрицательно">
-      <formula>NOT(ISERROR(SEARCH("отрицательно",F23)))</formula>
+  <conditionalFormatting sqref="F21:F23">
+    <cfRule type="containsText" dxfId="9" priority="18" operator="containsText" text="отрицательно">
+      <formula>NOT(ISERROR(SEARCH("отрицательно",F21)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F23">
-    <cfRule type="containsText" dxfId="4" priority="13" operator="containsText" text="сомнительно">
-      <formula>NOT(ISERROR(SEARCH("сомнительно",F23)))</formula>
+  <conditionalFormatting sqref="F21:F23">
+    <cfRule type="containsText" dxfId="8" priority="17" operator="containsText" text="отрицательно">
+      <formula>NOT(ISERROR(SEARCH("отрицательно",F21)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C23">
-    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Х">
-      <formula>NOT(ISERROR(SEARCH("Х",C23:C31)))</formula>
+  <conditionalFormatting sqref="F21:F23">
+    <cfRule type="containsText" dxfId="7" priority="16" operator="containsText" text="сомнительно">
+      <formula>NOT(ISERROR(SEARCH("сомнительно",F21)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C19:C21">
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Х">
-      <formula>NOT(ISERROR(SEARCH("Х",C19:C27)))</formula>
+  <conditionalFormatting sqref="F25">
+    <cfRule type="containsText" dxfId="6" priority="15" operator="containsText" text="отрицательно">
+      <formula>NOT(ISERROR(SEARCH("отрицательно",F25)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C14">
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Х">
-      <formula>NOT(ISERROR(SEARCH("Х",C14:C22)))</formula>
+  <conditionalFormatting sqref="F25">
+    <cfRule type="containsText" dxfId="5" priority="14" operator="containsText" text="отрицательно">
+      <formula>NOT(ISERROR(SEARCH("отрицательно",F25)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C15">
+  <conditionalFormatting sqref="F25">
+    <cfRule type="containsText" dxfId="4" priority="13" operator="containsText" text="сомнительно">
+      <formula>NOT(ISERROR(SEARCH("сомнительно",F25)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C25">
+    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Х">
+      <formula>NOT(ISERROR(SEARCH("Х",C25:C33)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C21:C23">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Х">
+      <formula>NOT(ISERROR(SEARCH("Х",C21:C29)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16">
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Х">
+      <formula>NOT(ISERROR(SEARCH("Х",C16:C24)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C17">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Х">
-      <formula>NOT(ISERROR(SEARCH("Х",C15:C23)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Х",C17:C25)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5054,7 +5073,7 @@
           <x14:formula1>
             <xm:f>Легенда!$C$2:$C$4</xm:f>
           </x14:formula1>
-          <xm:sqref>F12:F13 F34 F30 F7:F10 F24 F19</xm:sqref>
+          <xm:sqref>F14:F15 F36 F32 F9:F12 F26 F21</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{80AB261B-DD3F-47CD-AFA5-3DC903BA0952}">
           <x14:formula1>
@@ -5066,43 +5085,43 @@
           <x14:formula1>
             <xm:f>Легенда!$C$7:$C$8</xm:f>
           </x14:formula1>
-          <xm:sqref>F31:F38</xm:sqref>
+          <xm:sqref>F33:F40</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3E27E3ED-2DC6-41F1-A8BF-201219C93465}">
           <x14:formula1>
             <xm:f>Легенда!$A$8:$A$25</xm:f>
           </x14:formula1>
-          <xm:sqref>G2</xm:sqref>
+          <xm:sqref>G2:H2</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2F52BA69-CDA0-4FA1-8FA7-BC96A4D66567}">
           <x14:formula1>
             <xm:f>Легенда!$A$28:$A$83</xm:f>
           </x14:formula1>
-          <xm:sqref>H2</xm:sqref>
+          <xm:sqref>G3:H3</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B358EBC8-3958-4296-BF75-0A14C21AE495}">
           <x14:formula1>
             <xm:f>Легенда!$E$2:$E$3</xm:f>
           </x14:formula1>
-          <xm:sqref>F31:F38</xm:sqref>
+          <xm:sqref>F33:F40</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D2E7520F-9BA0-4387-B5CB-2D2E7EF2AE75}">
           <x14:formula1>
             <xm:f>Легенда!$F$2:$F$3</xm:f>
           </x14:formula1>
-          <xm:sqref>F30:F38 F4</xm:sqref>
+          <xm:sqref>F32:F40 F5</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EB10659D-7315-4E0F-8B01-B2D579B18932}">
           <x14:formula1>
             <xm:f>Легенда!$C$2:$C$5</xm:f>
           </x14:formula1>
-          <xm:sqref>F26:F29 F7 F11 F14:F15 F17 F19:F21 F23</xm:sqref>
+          <xm:sqref>F28:F31 F9 F13 F16:F17 F19 F21:F23 F25</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EB549AC4-151D-41D9-971D-BCE330D7864E}">
           <x14:formula1>
             <xm:f>Легенда!$G$2:$G$4</xm:f>
           </x14:formula1>
-          <xm:sqref>F5</xm:sqref>
+          <xm:sqref>F6:F7</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5113,19 +5132,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33D5ACCE-DA51-4F09-BED7-B024EC8702EE}">
   <dimension ref="A1:G83"/>
-  <sheetFormatPr defaultColWidth="14.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="14.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.44140625" style="7" customWidth="1"/>
-    <col min="2" max="2" width="3.5546875" style="7" customWidth="1"/>
-    <col min="3" max="3" width="14.21875" style="7"/>
-    <col min="4" max="4" width="4.44140625" style="7" customWidth="1"/>
-    <col min="5" max="5" width="14.21875" style="7"/>
-    <col min="6" max="6" width="14.21875" style="6"/>
-    <col min="7" max="7" width="29.44140625" style="6" customWidth="1"/>
-    <col min="8" max="16384" width="14.21875" style="6"/>
+    <col min="1" max="1" width="29.453125" style="7" customWidth="1"/>
+    <col min="2" max="2" width="3.54296875" style="7" customWidth="1"/>
+    <col min="3" max="3" width="14.1796875" style="7"/>
+    <col min="4" max="4" width="4.453125" style="7" customWidth="1"/>
+    <col min="5" max="5" width="14.1796875" style="7"/>
+    <col min="6" max="6" width="14.1796875" style="6"/>
+    <col min="7" max="7" width="29.453125" style="6" customWidth="1"/>
+    <col min="8" max="16384" width="14.1796875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>18</v>
       </c>
@@ -5142,7 +5161,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
         <v>19</v>
       </c>
@@ -5159,7 +5178,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
         <v>21</v>
       </c>
@@ -5176,7 +5195,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
         <v>24</v>
       </c>
@@ -5187,7 +5206,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
         <v>25</v>
       </c>
@@ -5195,10 +5214,10 @@
         <v>137</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="8"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
         <v>16</v>
       </c>
@@ -5210,8 +5229,8 @@
       </c>
       <c r="G7" s="7"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="33" t="s">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="34" t="s">
         <v>61</v>
       </c>
       <c r="C8" s="7" t="s">
@@ -5222,8 +5241,8 @@
       </c>
       <c r="G8" s="7"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="34" t="s">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="35" t="s">
         <v>41</v>
       </c>
       <c r="E9" s="7">
@@ -5231,383 +5250,383 @@
       </c>
       <c r="G9" s="7"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="34" t="s">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="35" t="s">
         <v>34</v>
       </c>
       <c r="G10" s="7"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="34" t="s">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="35" t="s">
         <v>62</v>
       </c>
       <c r="G11" s="7"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="34" t="s">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="35" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="34" t="s">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="35" t="s">
         <v>35</v>
       </c>
       <c r="G13" s="7"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="34" t="s">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="35" t="s">
         <v>42</v>
       </c>
       <c r="G14" s="7"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="34" t="s">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" s="35" t="s">
         <v>66</v>
       </c>
       <c r="G15" s="7"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="34" t="s">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" s="35" t="s">
         <v>67</v>
       </c>
       <c r="G16" s="7"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="34" t="s">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" s="35" t="s">
         <v>68</v>
       </c>
       <c r="G17" s="7"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="34" t="s">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" s="35" t="s">
         <v>63</v>
       </c>
       <c r="G18" s="7"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="34" t="s">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19" s="35" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="34" t="s">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20" s="35" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="34" t="s">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21" s="35" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="34" t="s">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22" s="35" t="s">
         <v>65</v>
       </c>
       <c r="G22" s="7"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="34" t="s">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A23" s="35" t="s">
         <v>39</v>
       </c>
       <c r="G23" s="7"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="34" t="s">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A24" s="35" t="s">
         <v>64</v>
       </c>
       <c r="G24" s="7"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="34" t="s">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A25" s="35" t="s">
         <v>43</v>
       </c>
       <c r="G25" s="7"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="35"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A26" s="36"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="36" t="s">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A28" s="37" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="36" t="s">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A29" s="37" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="36" t="s">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A30" s="37" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="36" t="s">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A31" s="37" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="36" t="s">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A32" s="37" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" s="36" t="s">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A33" s="37" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" s="36" t="s">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A34" s="37" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" s="36" t="s">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A35" s="37" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" s="36" t="s">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A36" s="37" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" s="36" t="s">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A37" s="37" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" s="36" t="s">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A38" s="37" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" s="36" t="s">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A39" s="37" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" s="36" t="s">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A40" s="37" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" s="36" t="s">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A41" s="37" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A42" s="36" t="s">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A42" s="37" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43" s="36" t="s">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A43" s="37" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A44" s="36" t="s">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A44" s="37" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A45" s="36" t="s">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A45" s="37" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A46" s="36" t="s">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A46" s="37" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A47" s="36" t="s">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A47" s="37" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A48" s="36" t="s">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A48" s="37" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49" s="36" t="s">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A49" s="37" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50" s="36" t="s">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A50" s="37" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" s="36" t="s">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A51" s="37" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A52" s="36" t="s">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A52" s="37" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A53" s="36" t="s">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A53" s="37" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A54" s="36" t="s">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A54" s="37" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A55" s="36" t="s">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A55" s="37" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A56" s="36" t="s">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A56" s="37" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A57" s="36" t="s">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A57" s="37" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A58" s="36" t="s">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A58" s="37" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A59" s="36" t="s">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A59" s="37" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A60" s="36" t="s">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A60" s="37" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A61" s="36" t="s">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A61" s="37" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="62" spans="1:1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="36" t="s">
+    <row r="62" spans="1:1" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="37" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A63" s="36" t="s">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A63" s="37" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A64" s="36" t="s">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A64" s="37" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A65" s="36" t="s">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A65" s="37" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A66" s="36" t="s">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A66" s="37" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A67" s="36" t="s">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A67" s="37" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A68" s="36" t="s">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A68" s="37" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A69" s="36" t="s">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A69" s="37" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A70" s="36" t="s">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A70" s="37" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A71" s="36" t="s">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A71" s="37" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A72" s="36" t="s">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A72" s="37" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A73" s="36" t="s">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A73" s="37" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A74" s="36" t="s">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A74" s="37" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A75" s="36" t="s">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A75" s="37" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A76" s="36" t="s">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A76" s="37" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A77" s="36" t="s">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A77" s="37" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A78" s="36" t="s">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A78" s="37" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A79" s="36" t="s">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A79" s="37" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A80" s="36" t="s">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A80" s="37" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A81" s="36" t="s">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A81" s="37" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A82" s="36" t="s">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A82" s="37" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A83" s="36" t="s">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A83" s="37" t="s">
         <v>123</v>
       </c>
     </row>
